--- a/data/review/openalex_review.xlsx
+++ b/data/review/openalex_review.xlsx
@@ -15761,7 +15761,7 @@
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>Put 'accepted' or 'rejected' in the Decision column. Accept at most one record per person: the one that is their main OpenAlex record. Leave a row blank to decide later. Put your name in 'Reviewed by' if you like; Notes is free text and is kept.</t>
+          <t>Put 'accepted' or 'rejected' in the Decision column. Accept EVERY record that is this person, and reject the ones that are not. OpenAlex often splits one author across several records, and we add a person's records together, so the question is only 'is this them?', never 'which one is the main one?'. Leave a row blank to decide later. Put your name in 'Reviewed by' if you like; Notes is free text and is kept.</t>
         </is>
       </c>
     </row>
@@ -15778,7 +15778,7 @@
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>OpenAlex often splits one author across several records. The matcher will not accept a winner while a substantive sibling record scores close behind, so these wait for a person to say which is the main one. That is why the rows are ordered by Works: the fullest record is usually the right one, and 'best match' marks the matcher's pick.</t>
+          <t>OpenAlex often splits one author across several records. The matcher will not accept on its own while a substantive sibling record scores close behind, so these wait for a person to say which records are theirs. Rows are ordered by Works, fullest first; 'best match' marks the matcher's pick, which is almost always one of theirs.</t>
         </is>
       </c>
     </row>

--- a/data/review/openalex_review.xlsx
+++ b/data/review/openalex_review.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="709" documentId="11_284333FFCD507A9B34BE53DE557A4504C07FE056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45179930-B5EF-491D-B86B-86631ED2958F}"/>
+  <xr:revisionPtr revIDLastSave="733" documentId="11_284333FFCD507A9B34BE53DE557A4504C07FE056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD226EFB-916A-4C7F-A67E-80BF57A15355}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3577" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="1125">
   <si>
     <t>Band</t>
   </si>
@@ -1585,7 +1585,7 @@
     <t>Daniel M. Abramson</t>
   </si>
   <si>
-    <t>unsure - i doubt it's him but not 100%</t>
+    <t>unsure - i doubt it's him but not 100%. the UW website is inaccessible and I can't find his CV</t>
   </si>
   <si>
     <t>A5060843627</t>
@@ -1915,6 +1915,9 @@
     <t>Kwame Nkrumah University of Science and Technology</t>
   </si>
   <si>
+    <t>I am fairly positive this is him, but not 100% sure</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
@@ -3188,6 +3191,9 @@
   </si>
   <si>
     <t>Balıkesir University</t>
+  </si>
+  <si>
+    <t>I think these are to the same profile - not him though</t>
   </si>
   <si>
     <t>648</t>
@@ -4324,7 +4330,7 @@
         <v>25</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
@@ -4383,7 +4389,7 @@
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="11" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="P9" s="11" t="s">
         <v>27</v>
@@ -5718,7 +5724,9 @@
         <v>0</v>
       </c>
       <c r="N33" s="3"/>
-      <c r="O33" s="5"/>
+      <c r="O33" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
       <c r="R33" s="6" t="s">
@@ -6615,12 +6623,16 @@
       <c r="N48" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="O48" s="11"/>
-      <c r="P48" s="11"/>
-      <c r="Q48" s="11"/>
-      <c r="R48" s="12" t="s">
-        <v>109</v>
-      </c>
+      <c r="O48" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="P48" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q48" s="21">
+        <v>46308</v>
+      </c>
+      <c r="R48" s="12"/>
       <c r="S48" s="13" t="s">
         <v>178</v>
       </c>
@@ -6667,7 +6679,9 @@
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
-      <c r="R49" s="6"/>
+      <c r="R49" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="S49" s="3" t="s">
         <v>178</v>
       </c>
@@ -12872,7 +12886,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="156" spans="1:21" ht="30.75">
+    <row r="156" spans="1:21" ht="60.75">
       <c r="A156" s="8" t="s">
         <v>422</v>
       </c>
@@ -14455,7 +14469,9 @@
         <v>0.09</v>
       </c>
       <c r="N182" s="13"/>
-      <c r="O182" s="11"/>
+      <c r="O182" s="11" t="s">
+        <v>38</v>
+      </c>
       <c r="P182" s="11"/>
       <c r="Q182" s="11"/>
       <c r="R182" s="12" t="s">
@@ -14689,7 +14705,9 @@
         <v>0.01</v>
       </c>
       <c r="N186" s="13"/>
-      <c r="O186" s="11"/>
+      <c r="O186" s="11" t="s">
+        <v>26</v>
+      </c>
       <c r="P186" s="11" t="s">
         <v>80</v>
       </c>
@@ -14697,16 +14715,16 @@
         <v>46305</v>
       </c>
       <c r="R186" s="12" t="s">
-        <v>524</v>
+        <v>626</v>
       </c>
       <c r="S186" s="13" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="T186" s="13" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="U186" s="14" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="187" spans="1:21">
@@ -14757,13 +14775,13 @@
         <v>482</v>
       </c>
       <c r="S187" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="T187" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="U187" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="188" spans="1:21">
@@ -14771,10 +14789,10 @@
         <v>422</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D188" s="9">
         <v>2030</v>
@@ -14783,10 +14801,10 @@
         <v>425</v>
       </c>
       <c r="F188" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G188" s="10" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H188" s="9">
         <v>1914</v>
@@ -14818,13 +14836,13 @@
       </c>
       <c r="R188" s="12"/>
       <c r="S188" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="T188" s="13" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="U188" s="14" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="189" spans="1:21">
@@ -14832,10 +14850,10 @@
         <v>422</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D189" s="9">
         <v>2030</v>
@@ -14844,10 +14862,10 @@
         <v>425</v>
       </c>
       <c r="F189" s="9" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H189" s="9">
         <v>3536</v>
@@ -14877,13 +14895,13 @@
       <c r="Q189" s="11"/>
       <c r="R189" s="12"/>
       <c r="S189" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="T189" s="13" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="U189" s="14" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="190" spans="1:21">
@@ -14891,10 +14909,10 @@
         <v>422</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D190" s="9">
         <v>2030</v>
@@ -14903,7 +14921,7 @@
         <v>425</v>
       </c>
       <c r="F190" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G190" s="10" t="s">
         <v>56</v>
@@ -14934,13 +14952,13 @@
       <c r="Q190" s="11"/>
       <c r="R190" s="12"/>
       <c r="S190" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="T190" s="13" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="U190" s="14" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="191" spans="1:21">
@@ -14948,10 +14966,10 @@
         <v>422</v>
       </c>
       <c r="B191" s="15" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C191" s="15" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D191" s="15">
         <v>2030</v>
@@ -14960,7 +14978,7 @@
         <v>425</v>
       </c>
       <c r="F191" s="15" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G191" s="16"/>
       <c r="H191" s="15">
@@ -14989,13 +15007,13 @@
       <c r="Q191" s="5"/>
       <c r="R191" s="6"/>
       <c r="S191" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="T191" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="U191" s="7" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="192" spans="1:21">
@@ -15003,10 +15021,10 @@
         <v>422</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C192" s="13" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D192" s="13">
         <v>1893</v>
@@ -15015,10 +15033,10 @@
         <v>425</v>
       </c>
       <c r="F192" s="13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G192" s="17" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H192" s="13">
         <v>1413</v>
@@ -15050,13 +15068,13 @@
       </c>
       <c r="R192" s="12"/>
       <c r="S192" s="13" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="T192" s="13" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="U192" s="14" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="193" spans="1:21">
@@ -15064,10 +15082,10 @@
         <v>422</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C193" s="13" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D193" s="13">
         <v>1893</v>
@@ -15076,7 +15094,7 @@
         <v>425</v>
       </c>
       <c r="F193" s="13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G193" s="17"/>
       <c r="H193" s="13">
@@ -15107,13 +15125,13 @@
       </c>
       <c r="R193" s="12"/>
       <c r="S193" s="13" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="T193" s="13" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="U193" s="14" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="194" spans="1:21">
@@ -15121,10 +15139,10 @@
         <v>422</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C194" s="13" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D194" s="13">
         <v>1893</v>
@@ -15133,10 +15151,10 @@
         <v>425</v>
       </c>
       <c r="F194" s="13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G194" s="17" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H194" s="13">
         <v>411</v>
@@ -15166,13 +15184,13 @@
       <c r="Q194" s="11"/>
       <c r="R194" s="12"/>
       <c r="S194" s="13" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="T194" s="13" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="U194" s="14" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="195" spans="1:21">
@@ -15180,10 +15198,10 @@
         <v>422</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D195" s="3">
         <v>1893</v>
@@ -15192,10 +15210,10 @@
         <v>425</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H195" s="3">
         <v>15</v>
@@ -15223,13 +15241,13 @@
       <c r="Q195" s="5"/>
       <c r="R195" s="6"/>
       <c r="S195" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="T195" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="U195" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="196" spans="1:21">
@@ -15237,7 +15255,7 @@
         <v>422</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>336</v>
@@ -15249,10 +15267,10 @@
         <v>425</v>
       </c>
       <c r="F196" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G196" s="10" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H196" s="9">
         <v>10</v>
@@ -15286,13 +15304,13 @@
       </c>
       <c r="R196" s="12"/>
       <c r="S196" s="13" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="T196" s="13" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="U196" s="14" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="197" spans="1:21">
@@ -15300,7 +15318,7 @@
         <v>422</v>
       </c>
       <c r="B197" s="15" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C197" s="15" t="s">
         <v>336</v>
@@ -15312,7 +15330,7 @@
         <v>425</v>
       </c>
       <c r="F197" s="15" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G197" s="16"/>
       <c r="H197" s="15">
@@ -15341,13 +15359,13 @@
       <c r="Q197" s="5"/>
       <c r="R197" s="6"/>
       <c r="S197" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="T197" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="U197" s="7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="198" spans="1:21">
@@ -15355,7 +15373,7 @@
         <v>422</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C198" s="13" t="s">
         <v>187</v>
@@ -15367,10 +15385,10 @@
         <v>425</v>
       </c>
       <c r="F198" s="13" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G198" s="17" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H198" s="13">
         <v>24</v>
@@ -15404,13 +15422,13 @@
       </c>
       <c r="R198" s="12"/>
       <c r="S198" s="13" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="T198" s="13" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="U198" s="14" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="199" spans="1:21">
@@ -15418,7 +15436,7 @@
         <v>422</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>187</v>
@@ -15430,7 +15448,7 @@
         <v>425</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G199" s="4"/>
       <c r="H199" s="3">
@@ -15452,20 +15470,22 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="N199" s="3"/>
-      <c r="O199" s="5"/>
+      <c r="O199" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="P199" s="5"/>
       <c r="Q199" s="5"/>
       <c r="R199" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="S199" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="T199" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="U199" s="7" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="200" spans="1:21">
@@ -15473,7 +15493,7 @@
         <v>422</v>
       </c>
       <c r="B200" s="15" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C200" s="15" t="s">
         <v>235</v>
@@ -15485,7 +15505,7 @@
         <v>425</v>
       </c>
       <c r="F200" s="15" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G200" s="16"/>
       <c r="H200" s="15">
@@ -15520,13 +15540,13 @@
         <v>482</v>
       </c>
       <c r="S200" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="T200" s="3" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="U200" s="7" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="201" spans="1:21">
@@ -15534,7 +15554,7 @@
         <v>422</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C201" s="13" t="s">
         <v>182</v>
@@ -15546,7 +15566,7 @@
         <v>425</v>
       </c>
       <c r="F201" s="13" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G201" s="17"/>
       <c r="H201" s="13">
@@ -15581,13 +15601,13 @@
         <v>482</v>
       </c>
       <c r="S201" s="13" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="T201" s="13" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="U201" s="14" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="202" spans="1:21">
@@ -15595,7 +15615,7 @@
         <v>422</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>182</v>
@@ -15607,7 +15627,7 @@
         <v>425</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G202" s="4"/>
       <c r="H202" s="3">
@@ -15636,13 +15656,13 @@
       <c r="Q202" s="5"/>
       <c r="R202" s="6"/>
       <c r="S202" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="T202" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="U202" s="7" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="203" spans="1:21">
@@ -15650,7 +15670,7 @@
         <v>422</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>424</v>
@@ -15662,7 +15682,7 @@
         <v>425</v>
       </c>
       <c r="F203" s="9" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G203" s="10"/>
       <c r="H203" s="9">
@@ -15695,13 +15715,13 @@
       </c>
       <c r="R203" s="12"/>
       <c r="S203" s="13" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T203" s="13" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="U203" s="14" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="204" spans="1:21">
@@ -15709,7 +15729,7 @@
         <v>422</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>424</v>
@@ -15721,7 +15741,7 @@
         <v>425</v>
       </c>
       <c r="F204" s="9" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G204" s="10"/>
       <c r="H204" s="9">
@@ -15752,13 +15772,13 @@
       <c r="Q204" s="11"/>
       <c r="R204" s="12"/>
       <c r="S204" s="13" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T204" s="13" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="U204" s="14" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="205" spans="1:21">
@@ -15766,7 +15786,7 @@
         <v>422</v>
       </c>
       <c r="B205" s="15" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C205" s="15" t="s">
         <v>424</v>
@@ -15778,7 +15798,7 @@
         <v>425</v>
       </c>
       <c r="F205" s="15" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G205" s="16"/>
       <c r="H205" s="15">
@@ -15807,13 +15827,13 @@
       <c r="Q205" s="5"/>
       <c r="R205" s="6"/>
       <c r="S205" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T205" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="U205" s="7" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="206" spans="1:21">
@@ -15821,10 +15841,10 @@
         <v>422</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D206" s="3">
         <v>863</v>
@@ -15833,10 +15853,10 @@
         <v>425</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H206" s="3">
         <v>54</v>
@@ -15870,13 +15890,13 @@
       </c>
       <c r="R206" s="6"/>
       <c r="S206" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="T206" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="U206" s="7" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="207" spans="1:21">
@@ -15884,10 +15904,10 @@
         <v>422</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C207" s="9" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D207" s="9">
         <v>551</v>
@@ -15896,7 +15916,7 @@
         <v>425</v>
       </c>
       <c r="F207" s="9" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G207" s="10"/>
       <c r="H207" s="9">
@@ -15929,13 +15949,13 @@
       </c>
       <c r="R207" s="12"/>
       <c r="S207" s="13" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="T207" s="13" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="U207" s="14" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="208" spans="1:21">
@@ -15943,10 +15963,10 @@
         <v>422</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C208" s="9" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D208" s="9">
         <v>551</v>
@@ -15955,10 +15975,10 @@
         <v>425</v>
       </c>
       <c r="F208" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G208" s="10" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H208" s="9">
         <v>80</v>
@@ -15988,13 +16008,13 @@
       <c r="Q208" s="11"/>
       <c r="R208" s="12"/>
       <c r="S208" s="13" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="T208" s="13" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="U208" s="14" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="209" spans="1:21">
@@ -16002,10 +16022,10 @@
         <v>422</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D209" s="9">
         <v>551</v>
@@ -16014,10 +16034,10 @@
         <v>425</v>
       </c>
       <c r="F209" s="9" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H209" s="9">
         <v>440</v>
@@ -16045,13 +16065,13 @@
       <c r="Q209" s="11"/>
       <c r="R209" s="12"/>
       <c r="S209" s="13" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="T209" s="13" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="U209" s="14" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="210" spans="1:21">
@@ -16059,10 +16079,10 @@
         <v>422</v>
       </c>
       <c r="B210" s="15" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C210" s="15" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D210" s="15">
         <v>551</v>
@@ -16071,7 +16091,7 @@
         <v>425</v>
       </c>
       <c r="F210" s="15" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G210" s="16"/>
       <c r="H210" s="15">
@@ -16100,13 +16120,13 @@
       <c r="Q210" s="5"/>
       <c r="R210" s="6"/>
       <c r="S210" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="T210" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="U210" s="7" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="211" spans="1:21">
@@ -16114,7 +16134,7 @@
         <v>422</v>
       </c>
       <c r="B211" s="13" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C211" s="13" t="s">
         <v>392</v>
@@ -16126,7 +16146,7 @@
         <v>425</v>
       </c>
       <c r="F211" s="13" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G211" s="17"/>
       <c r="H211" s="13">
@@ -16161,13 +16181,13 @@
         <v>482</v>
       </c>
       <c r="S211" s="13" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="T211" s="13" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="U211" s="14" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="212" spans="1:21">
@@ -16175,7 +16195,7 @@
         <v>422</v>
       </c>
       <c r="B212" s="13" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C212" s="13" t="s">
         <v>392</v>
@@ -16187,7 +16207,7 @@
         <v>425</v>
       </c>
       <c r="F212" s="13" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G212" s="17"/>
       <c r="H212" s="13">
@@ -16216,13 +16236,13 @@
       <c r="Q212" s="11"/>
       <c r="R212" s="12"/>
       <c r="S212" s="13" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="T212" s="13" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="U212" s="14" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="213" spans="1:21">
@@ -16230,7 +16250,7 @@
         <v>422</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>392</v>
@@ -16242,7 +16262,7 @@
         <v>425</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G213" s="4"/>
       <c r="H213" s="3">
@@ -16271,13 +16291,13 @@
       <c r="Q213" s="5"/>
       <c r="R213" s="6"/>
       <c r="S213" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="T213" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="U213" s="7" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="214" spans="1:21">
@@ -16285,7 +16305,7 @@
         <v>422</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C214" s="9" t="s">
         <v>360</v>
@@ -16297,7 +16317,7 @@
         <v>425</v>
       </c>
       <c r="F214" s="9" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G214" s="10"/>
       <c r="H214" s="9">
@@ -16326,13 +16346,13 @@
       <c r="Q214" s="11"/>
       <c r="R214" s="12"/>
       <c r="S214" s="13" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="T214" s="13" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="U214" s="14" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="215" spans="1:21">
@@ -16340,7 +16360,7 @@
         <v>422</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C215" s="9" t="s">
         <v>360</v>
@@ -16352,10 +16372,10 @@
         <v>425</v>
       </c>
       <c r="F215" s="9" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H215" s="9">
         <v>50</v>
@@ -16389,13 +16409,13 @@
       </c>
       <c r="R215" s="12"/>
       <c r="S215" s="13" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="T215" s="13" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="U215" s="14" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="216" spans="1:21">
@@ -16403,7 +16423,7 @@
         <v>422</v>
       </c>
       <c r="B216" s="15" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C216" s="15" t="s">
         <v>360</v>
@@ -16415,10 +16435,10 @@
         <v>425</v>
       </c>
       <c r="F216" s="15" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G216" s="16" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H216" s="15">
         <v>161</v>
@@ -16446,13 +16466,13 @@
       <c r="Q216" s="5"/>
       <c r="R216" s="6"/>
       <c r="S216" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="T216" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="U216" s="7" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="217" spans="1:21">
@@ -16460,7 +16480,7 @@
         <v>422</v>
       </c>
       <c r="B217" s="13" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C217" s="13" t="s">
         <v>392</v>
@@ -16472,10 +16492,10 @@
         <v>425</v>
       </c>
       <c r="F217" s="13" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G217" s="17" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H217" s="13">
         <v>192</v>
@@ -16509,13 +16529,13 @@
       </c>
       <c r="R217" s="12"/>
       <c r="S217" s="13" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="T217" s="13" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="U217" s="14" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="218" spans="1:21">
@@ -16523,7 +16543,7 @@
         <v>422</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C218" s="13" t="s">
         <v>392</v>
@@ -16535,7 +16555,7 @@
         <v>425</v>
       </c>
       <c r="F218" s="13" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="G218" s="17" t="s">
         <v>23</v>
@@ -16566,13 +16586,13 @@
         <v>524</v>
       </c>
       <c r="S218" s="13" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="T218" s="13" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="U218" s="14" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="219" spans="1:21">
@@ -16580,7 +16600,7 @@
         <v>422</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>392</v>
@@ -16592,7 +16612,7 @@
         <v>425</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="G219" s="4"/>
       <c r="H219" s="3">
@@ -16621,13 +16641,13 @@
       <c r="Q219" s="5"/>
       <c r="R219" s="6"/>
       <c r="S219" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="T219" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="U219" s="7" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="220" spans="1:21">
@@ -16635,10 +16655,10 @@
         <v>422</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C220" s="9" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D220" s="9">
         <v>2098</v>
@@ -16647,7 +16667,7 @@
         <v>425</v>
       </c>
       <c r="F220" s="9" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G220" s="10"/>
       <c r="H220" s="9">
@@ -16680,13 +16700,13 @@
       </c>
       <c r="R220" s="12"/>
       <c r="S220" s="13" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="T220" s="13" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="U220" s="14" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="221" spans="1:21">
@@ -16694,10 +16714,10 @@
         <v>422</v>
       </c>
       <c r="B221" s="15" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C221" s="15" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D221" s="15">
         <v>2098</v>
@@ -16706,7 +16726,7 @@
         <v>425</v>
       </c>
       <c r="F221" s="15" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G221" s="16"/>
       <c r="H221" s="15">
@@ -16737,13 +16757,13 @@
       <c r="Q221" s="5"/>
       <c r="R221" s="6"/>
       <c r="S221" s="3" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="T221" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="U221" s="7" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="222" spans="1:21">
@@ -16751,10 +16771,10 @@
         <v>422</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D222" s="3">
         <v>4</v>
@@ -16763,10 +16783,10 @@
         <v>425</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H222" s="3">
         <v>17</v>
@@ -16800,13 +16820,13 @@
       </c>
       <c r="R222" s="6"/>
       <c r="S222" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="T222" s="3" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="U222" s="7" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="223" spans="1:21">
@@ -16814,7 +16834,7 @@
         <v>422</v>
       </c>
       <c r="B223" s="15" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C223" s="15" t="s">
         <v>105</v>
@@ -16826,7 +16846,7 @@
         <v>425</v>
       </c>
       <c r="F223" s="15" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G223" s="16" t="s">
         <v>221</v>
@@ -16863,13 +16883,13 @@
       </c>
       <c r="R223" s="6"/>
       <c r="S223" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="T223" s="3" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="U223" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="224" spans="1:21">
@@ -16877,7 +16897,7 @@
         <v>422</v>
       </c>
       <c r="B224" s="13" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C224" s="13" t="s">
         <v>182</v>
@@ -16889,10 +16909,10 @@
         <v>425</v>
       </c>
       <c r="F224" s="13" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="G224" s="17" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H224" s="13">
         <v>304</v>
@@ -16926,13 +16946,13 @@
       </c>
       <c r="R224" s="12"/>
       <c r="S224" s="13" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="T224" s="13" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="U224" s="14" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="225" spans="1:21">
@@ -16940,7 +16960,7 @@
         <v>422</v>
       </c>
       <c r="B225" s="13" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C225" s="13" t="s">
         <v>182</v>
@@ -16952,7 +16972,7 @@
         <v>425</v>
       </c>
       <c r="F225" s="13" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="G225" s="17"/>
       <c r="H225" s="13">
@@ -16981,13 +17001,13 @@
       <c r="Q225" s="11"/>
       <c r="R225" s="12"/>
       <c r="S225" s="13" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="T225" s="13" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="U225" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="226" spans="1:21">
@@ -16995,7 +17015,7 @@
         <v>422</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>182</v>
@@ -17007,7 +17027,7 @@
         <v>425</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="G226" s="4"/>
       <c r="H226" s="3">
@@ -17036,13 +17056,13 @@
       <c r="Q226" s="5"/>
       <c r="R226" s="6"/>
       <c r="S226" s="3" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="T226" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="U226" s="7" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="227" spans="1:21">
@@ -17050,7 +17070,7 @@
         <v>422</v>
       </c>
       <c r="B227" s="15" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C227" s="15" t="s">
         <v>502</v>
@@ -17062,7 +17082,7 @@
         <v>425</v>
       </c>
       <c r="F227" s="15" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G227" s="16"/>
       <c r="H227" s="15">
@@ -17097,13 +17117,13 @@
       </c>
       <c r="R227" s="6"/>
       <c r="S227" s="3" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="T227" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="U227" s="7" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="228" spans="1:21">
@@ -17111,7 +17131,7 @@
         <v>422</v>
       </c>
       <c r="B228" s="13" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C228" s="13" t="s">
         <v>117</v>
@@ -17123,10 +17143,10 @@
         <v>425</v>
       </c>
       <c r="F228" s="13" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G228" s="17" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H228" s="13">
         <v>580</v>
@@ -17160,13 +17180,13 @@
       </c>
       <c r="R228" s="12"/>
       <c r="S228" s="13" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="T228" s="13" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="U228" s="14" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="229" spans="1:21">
@@ -17174,7 +17194,7 @@
         <v>422</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>117</v>
@@ -17186,7 +17206,7 @@
         <v>425</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G229" s="4"/>
       <c r="H229" s="3">
@@ -17215,13 +17235,13 @@
       <c r="Q229" s="5"/>
       <c r="R229" s="6"/>
       <c r="S229" s="3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="T229" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="U229" s="7" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="230" spans="1:21">
@@ -17229,7 +17249,7 @@
         <v>422</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C230" s="9" t="s">
         <v>350</v>
@@ -17241,10 +17261,10 @@
         <v>425</v>
       </c>
       <c r="F230" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G230" s="10" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H230" s="9">
         <v>199</v>
@@ -17267,7 +17287,9 @@
       <c r="N230" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="O230" s="11"/>
+      <c r="O230" s="11" t="s">
+        <v>26</v>
+      </c>
       <c r="P230" s="11" t="s">
         <v>80</v>
       </c>
@@ -17278,13 +17300,13 @@
         <v>524</v>
       </c>
       <c r="S230" s="13" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="T230" s="13" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="U230" s="14" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="231" spans="1:21">
@@ -17292,7 +17314,7 @@
         <v>422</v>
       </c>
       <c r="B231" s="15" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C231" s="15" t="s">
         <v>350</v>
@@ -17304,7 +17326,7 @@
         <v>425</v>
       </c>
       <c r="F231" s="15" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="G231" s="16"/>
       <c r="H231" s="15">
@@ -17333,13 +17355,13 @@
         <v>482</v>
       </c>
       <c r="S231" s="3" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="T231" s="3" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="U231" s="7" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="232" spans="1:21">
@@ -17347,10 +17369,10 @@
         <v>422</v>
       </c>
       <c r="B232" s="13" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C232" s="13" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D232" s="13">
         <v>100</v>
@@ -17359,10 +17381,10 @@
         <v>425</v>
       </c>
       <c r="F232" s="13" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="G232" s="17" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H232" s="13">
         <v>152</v>
@@ -17394,13 +17416,13 @@
       </c>
       <c r="R232" s="12"/>
       <c r="S232" s="13" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="T232" s="13" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="U232" s="14" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="233" spans="1:21">
@@ -17408,10 +17430,10 @@
         <v>422</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D233" s="3">
         <v>100</v>
@@ -17420,10 +17442,10 @@
         <v>425</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H233" s="3">
         <v>48</v>
@@ -17453,13 +17475,13 @@
       <c r="Q233" s="5"/>
       <c r="R233" s="6"/>
       <c r="S233" s="3" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="T233" s="3" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="U233" s="7" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="234" spans="1:21">
@@ -17467,7 +17489,7 @@
         <v>422</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C234" s="9" t="s">
         <v>140</v>
@@ -17479,7 +17501,7 @@
         <v>425</v>
       </c>
       <c r="F234" s="9" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="G234" s="10" t="s">
         <v>540</v>
@@ -17514,13 +17536,13 @@
       </c>
       <c r="R234" s="12"/>
       <c r="S234" s="13" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="T234" s="13" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="U234" s="14" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="235" spans="1:21">
@@ -17528,7 +17550,7 @@
         <v>422</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C235" s="9" t="s">
         <v>140</v>
@@ -17540,7 +17562,7 @@
         <v>425</v>
       </c>
       <c r="F235" s="9" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="G235" s="10"/>
       <c r="H235" s="9">
@@ -17569,13 +17591,13 @@
       <c r="Q235" s="11"/>
       <c r="R235" s="12"/>
       <c r="S235" s="13" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="T235" s="13" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="U235" s="14" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="236" spans="1:21">
@@ -17583,7 +17605,7 @@
         <v>422</v>
       </c>
       <c r="B236" s="15" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C236" s="15" t="s">
         <v>140</v>
@@ -17595,10 +17617,10 @@
         <v>425</v>
       </c>
       <c r="F236" s="15" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="G236" s="16" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H236" s="15">
         <v>42</v>
@@ -17628,13 +17650,13 @@
       <c r="Q236" s="5"/>
       <c r="R236" s="6"/>
       <c r="S236" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="T236" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="U236" s="7" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="237" spans="1:21">
@@ -17642,7 +17664,7 @@
         <v>422</v>
       </c>
       <c r="B237" s="13" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C237" s="13" t="s">
         <v>207</v>
@@ -17654,10 +17676,10 @@
         <v>425</v>
       </c>
       <c r="F237" s="13" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="G237" s="17" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H237" s="13">
         <v>83</v>
@@ -17689,13 +17711,13 @@
       </c>
       <c r="R237" s="12"/>
       <c r="S237" s="13" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="T237" s="13" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="U237" s="14" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="238" spans="1:21">
@@ -17703,7 +17725,7 @@
         <v>422</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>207</v>
@@ -17715,10 +17737,10 @@
         <v>425</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H238" s="3">
         <v>8</v>
@@ -17748,13 +17770,13 @@
       <c r="Q238" s="5"/>
       <c r="R238" s="6"/>
       <c r="S238" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="T238" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="U238" s="7" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="239" spans="1:21">
@@ -17762,10 +17784,10 @@
         <v>422</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C239" s="9" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D239" s="9">
         <v>91</v>
@@ -17774,10 +17796,10 @@
         <v>425</v>
       </c>
       <c r="F239" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G239" s="10" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H239" s="9">
         <v>26</v>
@@ -17809,13 +17831,13 @@
       </c>
       <c r="R239" s="12"/>
       <c r="S239" s="13" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="T239" s="13" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="U239" s="14" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="240" spans="1:21">
@@ -17823,10 +17845,10 @@
         <v>422</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C240" s="9" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D240" s="9">
         <v>91</v>
@@ -17835,10 +17857,10 @@
         <v>425</v>
       </c>
       <c r="F240" s="9" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G240" s="10" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H240" s="9">
         <v>83</v>
@@ -17866,13 +17888,13 @@
       <c r="Q240" s="11"/>
       <c r="R240" s="12"/>
       <c r="S240" s="13" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="T240" s="13" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="U240" s="14" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="241" spans="1:21">
@@ -17880,10 +17902,10 @@
         <v>422</v>
       </c>
       <c r="B241" s="15" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C241" s="15" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D241" s="15">
         <v>91</v>
@@ -17892,7 +17914,7 @@
         <v>425</v>
       </c>
       <c r="F241" s="15" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G241" s="16" t="s">
         <v>606</v>
@@ -17918,20 +17940,22 @@
       <c r="N241" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="O241" s="5"/>
+      <c r="O241" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="P241" s="5"/>
       <c r="Q241" s="5"/>
       <c r="R241" s="6" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="S241" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="T241" s="3" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="U241" s="7" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="242" spans="1:21">
@@ -17939,7 +17963,7 @@
         <v>422</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>606</v>
@@ -17951,7 +17975,7 @@
         <v>425</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G242" s="4"/>
       <c r="H242" s="3">
@@ -17986,13 +18010,13 @@
       </c>
       <c r="R242" s="6"/>
       <c r="S242" s="3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="T242" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="U242" s="7" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="243" spans="1:21">
@@ -18000,10 +18024,10 @@
         <v>422</v>
       </c>
       <c r="B243" s="15" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C243" s="15" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D243" s="15">
         <v>1556</v>
@@ -18012,10 +18036,10 @@
         <v>425</v>
       </c>
       <c r="F243" s="15" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G243" s="16" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H243" s="15">
         <v>1</v>
@@ -18046,16 +18070,16 @@
         <v>46307</v>
       </c>
       <c r="R243" s="6" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="S243" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="T243" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="U243" s="7" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="244" spans="1:21">
@@ -18063,7 +18087,7 @@
         <v>422</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>508</v>
@@ -18075,7 +18099,7 @@
         <v>425</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G244" s="4"/>
       <c r="H244" s="3">
@@ -18108,13 +18132,13 @@
         <v>482</v>
       </c>
       <c r="S244" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="T244" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="U244" s="7" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="245" spans="1:21">
@@ -18122,10 +18146,10 @@
         <v>422</v>
       </c>
       <c r="B245" s="9" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C245" s="9" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D245" s="9">
         <v>1042</v>
@@ -18134,7 +18158,7 @@
         <v>425</v>
       </c>
       <c r="F245" s="9" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G245" s="10"/>
       <c r="H245" s="9">
@@ -18169,13 +18193,13 @@
         <v>482</v>
       </c>
       <c r="S245" s="13" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="T245" s="13" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="U245" s="14" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="246" spans="1:21">
@@ -18183,10 +18207,10 @@
         <v>422</v>
       </c>
       <c r="B246" s="15" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C246" s="15" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D246" s="15">
         <v>1042</v>
@@ -18195,7 +18219,7 @@
         <v>425</v>
       </c>
       <c r="F246" s="15" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G246" s="16"/>
       <c r="H246" s="15">
@@ -18224,13 +18248,13 @@
         <v>482</v>
       </c>
       <c r="S246" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="T246" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="U246" s="7" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="247" spans="1:21">
@@ -18238,10 +18262,10 @@
         <v>422</v>
       </c>
       <c r="B247" s="13" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C247" s="13" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D247" s="13">
         <v>0</v>
@@ -18250,7 +18274,7 @@
         <v>425</v>
       </c>
       <c r="F247" s="13" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G247" s="17"/>
       <c r="H247" s="13">
@@ -18281,13 +18305,13 @@
       </c>
       <c r="R247" s="12"/>
       <c r="S247" s="13" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="T247" s="13" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="U247" s="14" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="248" spans="1:21">
@@ -18295,10 +18319,10 @@
         <v>422</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C248" s="13" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D248" s="13">
         <v>0</v>
@@ -18307,10 +18331,10 @@
         <v>425</v>
       </c>
       <c r="F248" s="13" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G248" s="17" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H248" s="13">
         <v>40</v>
@@ -18336,13 +18360,13 @@
       <c r="Q248" s="11"/>
       <c r="R248" s="12"/>
       <c r="S248" s="13" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="T248" s="13" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="U248" s="14" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="249" spans="1:21">
@@ -18350,10 +18374,10 @@
         <v>422</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D249" s="3">
         <v>0</v>
@@ -18362,10 +18386,10 @@
         <v>425</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H249" s="3">
         <v>16</v>
@@ -18393,13 +18417,13 @@
       <c r="Q249" s="5"/>
       <c r="R249" s="6"/>
       <c r="S249" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="T249" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="U249" s="7" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="250" spans="1:21">
@@ -18407,7 +18431,7 @@
         <v>422</v>
       </c>
       <c r="B250" s="15" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C250" s="15" t="s">
         <v>360</v>
@@ -18419,7 +18443,7 @@
         <v>425</v>
       </c>
       <c r="F250" s="15" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G250" s="16"/>
       <c r="H250" s="15">
@@ -18454,13 +18478,13 @@
         <v>482</v>
       </c>
       <c r="S250" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="T250" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="U250" s="7" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="251" spans="1:21">
@@ -18468,7 +18492,7 @@
         <v>422</v>
       </c>
       <c r="B251" s="13" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C251" s="13" t="s">
         <v>606</v>
@@ -18480,7 +18504,7 @@
         <v>425</v>
       </c>
       <c r="F251" s="13" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G251" s="17"/>
       <c r="H251" s="13">
@@ -18512,16 +18536,16 @@
         <v>46307</v>
       </c>
       <c r="R251" s="12" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="S251" s="13" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="T251" s="13" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="U251" s="14" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="252" spans="1:21">
@@ -18529,7 +18553,7 @@
         <v>422</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>606</v>
@@ -18541,7 +18565,7 @@
         <v>425</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G252" s="4"/>
       <c r="H252" s="3">
@@ -18570,13 +18594,13 @@
       <c r="Q252" s="5"/>
       <c r="R252" s="6"/>
       <c r="S252" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="T252" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="U252" s="7" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="253" spans="1:21">
@@ -18584,10 +18608,10 @@
         <v>422</v>
       </c>
       <c r="B253" s="15" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C253" s="15" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D253" s="15">
         <v>252</v>
@@ -18596,10 +18620,10 @@
         <v>425</v>
       </c>
       <c r="F253" s="15" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G253" s="16" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H253" s="15">
         <v>102</v>
@@ -18633,13 +18657,13 @@
       </c>
       <c r="R253" s="6"/>
       <c r="S253" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="T253" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="U253" s="7" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="254" spans="1:21">
@@ -18647,10 +18671,10 @@
         <v>422</v>
       </c>
       <c r="B254" s="13" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C254" s="13" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D254" s="13">
         <v>33</v>
@@ -18659,7 +18683,7 @@
         <v>425</v>
       </c>
       <c r="F254" s="13" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G254" s="17"/>
       <c r="H254" s="13">
@@ -18694,13 +18718,13 @@
       </c>
       <c r="R254" s="12"/>
       <c r="S254" s="13" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="T254" s="13" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U254" s="14" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="255" spans="1:21">
@@ -18708,10 +18732,10 @@
         <v>422</v>
       </c>
       <c r="B255" s="13" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C255" s="13" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D255" s="13">
         <v>33</v>
@@ -18720,10 +18744,10 @@
         <v>425</v>
       </c>
       <c r="F255" s="13" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G255" s="17" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H255" s="13">
         <v>11</v>
@@ -18751,13 +18775,13 @@
       <c r="Q255" s="11"/>
       <c r="R255" s="12"/>
       <c r="S255" s="13" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="T255" s="13" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="U255" s="14" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="256" spans="1:21">
@@ -18765,10 +18789,10 @@
         <v>422</v>
       </c>
       <c r="B256" s="13" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C256" s="13" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D256" s="13">
         <v>33</v>
@@ -18777,7 +18801,7 @@
         <v>425</v>
       </c>
       <c r="F256" s="13" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G256" s="17"/>
       <c r="H256" s="13">
@@ -18799,20 +18823,22 @@
         <v>0.3</v>
       </c>
       <c r="N256" s="13"/>
-      <c r="O256" s="11"/>
+      <c r="O256" s="11" t="s">
+        <v>38</v>
+      </c>
       <c r="P256" s="11"/>
       <c r="Q256" s="11"/>
       <c r="R256" s="12" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="S256" s="13" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="T256" s="13" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="U256" s="14" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="257" spans="1:21">
@@ -18820,10 +18846,10 @@
         <v>422</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D257" s="3">
         <v>33</v>
@@ -18832,7 +18858,7 @@
         <v>425</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="G257" s="4"/>
       <c r="H257" s="3">
@@ -18861,13 +18887,13 @@
       <c r="Q257" s="5"/>
       <c r="R257" s="6"/>
       <c r="S257" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="T257" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="U257" s="7" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="258" spans="1:21">
@@ -18875,7 +18901,7 @@
         <v>422</v>
       </c>
       <c r="B258" s="9" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C258" s="9" t="s">
         <v>227</v>
@@ -18887,7 +18913,7 @@
         <v>425</v>
       </c>
       <c r="F258" s="9" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G258" s="10"/>
       <c r="H258" s="9">
@@ -18920,13 +18946,13 @@
       </c>
       <c r="R258" s="12"/>
       <c r="S258" s="13" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="T258" s="13" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="U258" s="14" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="259" spans="1:21">
@@ -18934,7 +18960,7 @@
         <v>422</v>
       </c>
       <c r="B259" s="15" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C259" s="15" t="s">
         <v>227</v>
@@ -18946,7 +18972,7 @@
         <v>425</v>
       </c>
       <c r="F259" s="15" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G259" s="16"/>
       <c r="H259" s="15">
@@ -18977,13 +19003,13 @@
       <c r="Q259" s="5"/>
       <c r="R259" s="6"/>
       <c r="S259" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="T259" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="U259" s="7" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="260" spans="1:21">
@@ -18991,7 +19017,7 @@
         <v>422</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>235</v>
@@ -19003,7 +19029,7 @@
         <v>425</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G260" s="4"/>
       <c r="H260" s="3">
@@ -19038,13 +19064,13 @@
       </c>
       <c r="R260" s="6"/>
       <c r="S260" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="T260" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="U260" s="7" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="261" spans="1:21" ht="30.75">
@@ -19052,10 +19078,10 @@
         <v>422</v>
       </c>
       <c r="B261" s="15" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C261" s="15" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D261" s="15">
         <v>0</v>
@@ -19064,10 +19090,10 @@
         <v>425</v>
       </c>
       <c r="F261" s="15" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G261" s="16" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H261" s="15">
         <v>65</v>
@@ -19098,16 +19124,16 @@
         <v>46307</v>
       </c>
       <c r="R261" s="6" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="S261" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="T261" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="U261" s="7" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="262" spans="1:21">
@@ -19115,7 +19141,7 @@
         <v>422</v>
       </c>
       <c r="B262" s="13" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C262" s="13" t="s">
         <v>573</v>
@@ -19127,10 +19153,10 @@
         <v>425</v>
       </c>
       <c r="F262" s="13" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G262" s="17" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H262" s="13">
         <v>10</v>
@@ -19164,13 +19190,13 @@
       </c>
       <c r="R262" s="12"/>
       <c r="S262" s="13" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="T262" s="13" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="U262" s="14" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="263" spans="1:21">
@@ -19178,7 +19204,7 @@
         <v>422</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>573</v>
@@ -19190,7 +19216,7 @@
         <v>425</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G263" s="4" t="s">
         <v>218</v>
@@ -19221,13 +19247,13 @@
       <c r="Q263" s="5"/>
       <c r="R263" s="6"/>
       <c r="S263" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="T263" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="U263" s="7" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="264" spans="1:21">
@@ -19235,10 +19261,10 @@
         <v>422</v>
       </c>
       <c r="B264" s="9" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C264" s="9" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D264" s="9">
         <v>0</v>
@@ -19247,7 +19273,7 @@
         <v>425</v>
       </c>
       <c r="F264" s="9" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G264" s="10"/>
       <c r="H264" s="9">
@@ -19278,13 +19304,13 @@
       </c>
       <c r="R264" s="12"/>
       <c r="S264" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="T264" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="U264" s="14" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="265" spans="1:21">
@@ -19292,10 +19318,10 @@
         <v>422</v>
       </c>
       <c r="B265" s="9" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C265" s="9" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D265" s="9">
         <v>0</v>
@@ -19304,10 +19330,10 @@
         <v>425</v>
       </c>
       <c r="F265" s="9" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G265" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H265" s="9">
         <v>91</v>
@@ -19335,13 +19361,13 @@
       <c r="Q265" s="11"/>
       <c r="R265" s="12"/>
       <c r="S265" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="T265" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="U265" s="14" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="266" spans="1:21">
@@ -19349,10 +19375,10 @@
         <v>422</v>
       </c>
       <c r="B266" s="15" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C266" s="15" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D266" s="15">
         <v>0</v>
@@ -19361,10 +19387,10 @@
         <v>425</v>
       </c>
       <c r="F266" s="15" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G266" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H266" s="15">
         <v>122</v>
@@ -19390,13 +19416,13 @@
       <c r="Q266" s="5"/>
       <c r="R266" s="6"/>
       <c r="S266" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="T266" s="3" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="U266" s="7" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="267" spans="1:21">
@@ -19404,7 +19430,7 @@
         <v>422</v>
       </c>
       <c r="B267" s="13" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C267" s="13" t="s">
         <v>72</v>
@@ -19416,10 +19442,10 @@
         <v>425</v>
       </c>
       <c r="F267" s="13" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G267" s="17" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H267" s="13">
         <v>8246</v>
@@ -19453,13 +19479,13 @@
       </c>
       <c r="R267" s="12"/>
       <c r="S267" s="13" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="T267" s="13" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="U267" s="14" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="268" spans="1:21">
@@ -19467,7 +19493,7 @@
         <v>422</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C268" s="13" t="s">
         <v>72</v>
@@ -19479,10 +19505,10 @@
         <v>425</v>
       </c>
       <c r="F268" s="13" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G268" s="17" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H268" s="13">
         <v>390</v>
@@ -19510,13 +19536,13 @@
       <c r="Q268" s="11"/>
       <c r="R268" s="12"/>
       <c r="S268" s="13" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="T268" s="13" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="U268" s="14" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="269" spans="1:21">
@@ -19524,7 +19550,7 @@
         <v>422</v>
       </c>
       <c r="B269" s="13" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C269" s="13" t="s">
         <v>72</v>
@@ -19536,10 +19562,10 @@
         <v>425</v>
       </c>
       <c r="F269" s="13" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G269" s="17" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H269" s="13">
         <v>760</v>
@@ -19567,13 +19593,13 @@
       <c r="Q269" s="11"/>
       <c r="R269" s="12"/>
       <c r="S269" s="13" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="T269" s="13" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="U269" s="14" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="270" spans="1:21">
@@ -19581,7 +19607,7 @@
         <v>422</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C270" s="3" t="s">
         <v>72</v>
@@ -19593,7 +19619,7 @@
         <v>425</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="G270" s="4"/>
       <c r="H270" s="3">
@@ -19622,13 +19648,13 @@
       <c r="Q270" s="5"/>
       <c r="R270" s="6"/>
       <c r="S270" s="3" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="T270" s="3" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="U270" s="7" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="271" spans="1:21">
@@ -19636,10 +19662,10 @@
         <v>422</v>
       </c>
       <c r="B271" s="15" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C271" s="15" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D271" s="15">
         <v>2233</v>
@@ -19648,7 +19674,7 @@
         <v>425</v>
       </c>
       <c r="F271" s="15" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G271" s="16"/>
       <c r="H271" s="15">
@@ -19683,13 +19709,13 @@
         <v>482</v>
       </c>
       <c r="S271" s="3" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="T271" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="U271" s="7" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="272" spans="1:21">
@@ -19697,10 +19723,10 @@
         <v>422</v>
       </c>
       <c r="B272" s="13" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C272" s="13" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D272" s="13">
         <v>201</v>
@@ -19709,7 +19735,7 @@
         <v>425</v>
       </c>
       <c r="F272" s="13" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G272" s="17" t="s">
         <v>235</v>
@@ -19744,13 +19770,13 @@
       </c>
       <c r="R272" s="12"/>
       <c r="S272" s="13" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="T272" s="13" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="U272" s="14" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="273" spans="1:21">
@@ -19758,10 +19784,10 @@
         <v>422</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D273" s="3">
         <v>201</v>
@@ -19770,7 +19796,7 @@
         <v>425</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G273" s="4" t="s">
         <v>419</v>
@@ -19796,20 +19822,22 @@
       <c r="N273" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="O273" s="5"/>
+      <c r="O273" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="P273" s="5"/>
       <c r="Q273" s="5"/>
       <c r="R273" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="S273" s="3" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="T273" s="3" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="U273" s="7" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="274" spans="1:21">
@@ -19817,7 +19845,7 @@
         <v>422</v>
       </c>
       <c r="B274" s="9" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C274" s="9" t="s">
         <v>72</v>
@@ -19829,10 +19857,10 @@
         <v>425</v>
       </c>
       <c r="F274" s="9" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="G274" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H274" s="9">
         <v>509</v>
@@ -19864,13 +19892,13 @@
       </c>
       <c r="R274" s="12"/>
       <c r="S274" s="13" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="T274" s="13" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="U274" s="14" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="275" spans="1:21">
@@ -19878,7 +19906,7 @@
         <v>422</v>
       </c>
       <c r="B275" s="15" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C275" s="15" t="s">
         <v>72</v>
@@ -19890,10 +19918,10 @@
         <v>425</v>
       </c>
       <c r="F275" s="15" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="G275" s="16" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H275" s="15">
         <v>4</v>
@@ -19923,13 +19951,13 @@
       <c r="Q275" s="5"/>
       <c r="R275" s="6"/>
       <c r="S275" s="3" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="T275" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="U275" s="7" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="276" spans="1:21">
@@ -19937,10 +19965,10 @@
         <v>422</v>
       </c>
       <c r="B276" s="13" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C276" s="13" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D276" s="13">
         <v>194</v>
@@ -19949,10 +19977,10 @@
         <v>425</v>
       </c>
       <c r="F276" s="13" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G276" s="17" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H276" s="13">
         <v>29</v>
@@ -19984,13 +20012,13 @@
       </c>
       <c r="R276" s="12"/>
       <c r="S276" s="13" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="T276" s="13" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="U276" s="14" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="277" spans="1:21">
@@ -19998,10 +20026,10 @@
         <v>422</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D277" s="3">
         <v>194</v>
@@ -20010,10 +20038,10 @@
         <v>425</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H277" s="3">
         <v>45</v>
@@ -20043,13 +20071,13 @@
       <c r="Q277" s="5"/>
       <c r="R277" s="6"/>
       <c r="S277" s="3" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="T277" s="3" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="U277" s="7" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="278" spans="1:21">
@@ -20057,10 +20085,10 @@
         <v>422</v>
       </c>
       <c r="B278" s="9" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C278" s="9" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D278" s="9">
         <v>6</v>
@@ -20069,10 +20097,10 @@
         <v>425</v>
       </c>
       <c r="F278" s="9" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="G278" s="10" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H278" s="9">
         <v>66</v>
@@ -20106,13 +20134,13 @@
       </c>
       <c r="R278" s="12"/>
       <c r="S278" s="13" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="T278" s="13" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="U278" s="14" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="279" spans="1:21">
@@ -20120,10 +20148,10 @@
         <v>422</v>
       </c>
       <c r="B279" s="15" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C279" s="15" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D279" s="15">
         <v>6</v>
@@ -20132,7 +20160,7 @@
         <v>425</v>
       </c>
       <c r="F279" s="15" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="G279" s="16"/>
       <c r="H279" s="15">
@@ -20161,13 +20189,13 @@
       <c r="Q279" s="5"/>
       <c r="R279" s="6"/>
       <c r="S279" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="T279" s="3" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="U279" s="7" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="280" spans="1:21">
@@ -20175,7 +20203,7 @@
         <v>422</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>424</v>
@@ -20187,10 +20215,10 @@
         <v>425</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="G280" s="4" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H280" s="3">
         <v>47</v>
@@ -20224,13 +20252,13 @@
       </c>
       <c r="R280" s="6"/>
       <c r="S280" s="3" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="T280" s="3" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="U280" s="7" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="281" spans="1:21">
@@ -20238,7 +20266,7 @@
         <v>422</v>
       </c>
       <c r="B281" s="15" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C281" s="15" t="s">
         <v>72</v>
@@ -20250,7 +20278,7 @@
         <v>425</v>
       </c>
       <c r="F281" s="15" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="G281" s="16"/>
       <c r="H281" s="15">
@@ -20274,7 +20302,9 @@
       <c r="N281" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="O281" s="5"/>
+      <c r="O281" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="P281" s="5" t="s">
         <v>80</v>
       </c>
@@ -20285,13 +20315,13 @@
         <v>524</v>
       </c>
       <c r="S281" s="3" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="T281" s="3" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="U281" s="7" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="282" spans="1:21">
@@ -20299,10 +20329,10 @@
         <v>422</v>
       </c>
       <c r="B282" s="13" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C282" s="13" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D282" s="13">
         <v>1109</v>
@@ -20311,10 +20341,10 @@
         <v>425</v>
       </c>
       <c r="F282" s="13" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G282" s="17" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H282" s="13">
         <v>908</v>
@@ -20348,13 +20378,13 @@
       </c>
       <c r="R282" s="12"/>
       <c r="S282" s="13" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="T282" s="13" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="U282" s="14" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="283" spans="1:21">
@@ -20362,10 +20392,10 @@
         <v>422</v>
       </c>
       <c r="B283" s="13" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C283" s="13" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D283" s="13">
         <v>1109</v>
@@ -20374,10 +20404,10 @@
         <v>425</v>
       </c>
       <c r="F283" s="13" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="G283" s="17" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H283" s="13">
         <v>647</v>
@@ -20405,13 +20435,13 @@
       <c r="Q283" s="11"/>
       <c r="R283" s="12"/>
       <c r="S283" s="13" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="T283" s="13" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="U283" s="14" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="284" spans="1:21">
@@ -20419,10 +20449,10 @@
         <v>422</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D284" s="3">
         <v>1109</v>
@@ -20431,7 +20461,7 @@
         <v>425</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="G284" s="4"/>
       <c r="H284" s="3">
@@ -20460,13 +20490,13 @@
       <c r="Q284" s="5"/>
       <c r="R284" s="6"/>
       <c r="S284" s="3" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="T284" s="3" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="U284" s="7" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="285" spans="1:21">
@@ -20474,10 +20504,10 @@
         <v>422</v>
       </c>
       <c r="B285" s="9" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C285" s="9" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D285" s="9">
         <v>3964</v>
@@ -20486,10 +20516,10 @@
         <v>425</v>
       </c>
       <c r="F285" s="9" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="G285" s="10" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H285" s="9">
         <v>10137</v>
@@ -20520,16 +20550,16 @@
         <v>46307</v>
       </c>
       <c r="R285" s="12" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="S285" s="13" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="T285" s="13" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="U285" s="14" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="286" spans="1:21">
@@ -20537,10 +20567,10 @@
         <v>422</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C286" s="9" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D286" s="9">
         <v>3964</v>
@@ -20549,10 +20579,10 @@
         <v>425</v>
       </c>
       <c r="F286" s="9" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="G286" s="10" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H286" s="9">
         <v>2670</v>
@@ -20582,13 +20612,13 @@
       <c r="Q286" s="11"/>
       <c r="R286" s="12"/>
       <c r="S286" s="13" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="T286" s="13" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="U286" s="14" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="287" spans="1:21">
@@ -20596,10 +20626,10 @@
         <v>422</v>
       </c>
       <c r="B287" s="9" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C287" s="9" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D287" s="9">
         <v>3964</v>
@@ -20608,10 +20638,10 @@
         <v>425</v>
       </c>
       <c r="F287" s="9" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="G287" s="10" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H287" s="9">
         <v>2102</v>
@@ -20639,13 +20669,13 @@
       <c r="Q287" s="11"/>
       <c r="R287" s="12"/>
       <c r="S287" s="13" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="T287" s="13" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="U287" s="14" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="288" spans="1:21">
@@ -20653,10 +20683,10 @@
         <v>422</v>
       </c>
       <c r="B288" s="15" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C288" s="15" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D288" s="15">
         <v>3964</v>
@@ -20665,10 +20695,10 @@
         <v>425</v>
       </c>
       <c r="F288" s="15" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G288" s="16" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H288" s="15">
         <v>2679</v>
@@ -20696,13 +20726,13 @@
       <c r="Q288" s="5"/>
       <c r="R288" s="6"/>
       <c r="S288" s="3" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="T288" s="3" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="U288" s="7" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="289" spans="1:21">
@@ -20710,7 +20740,7 @@
         <v>422</v>
       </c>
       <c r="B289" s="13" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C289" s="13" t="s">
         <v>336</v>
@@ -20722,10 +20752,10 @@
         <v>425</v>
       </c>
       <c r="F289" s="13" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="G289" s="17" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H289" s="13">
         <v>1175</v>
@@ -20757,13 +20787,13 @@
       </c>
       <c r="R289" s="12"/>
       <c r="S289" s="13" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="T289" s="13" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="U289" s="14" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="290" spans="1:21">
@@ -20771,7 +20801,7 @@
         <v>422</v>
       </c>
       <c r="B290" s="13" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C290" s="13" t="s">
         <v>336</v>
@@ -20783,10 +20813,10 @@
         <v>425</v>
       </c>
       <c r="F290" s="13" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="G290" s="17" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H290" s="13">
         <v>1</v>
@@ -20814,13 +20844,13 @@
       <c r="Q290" s="11"/>
       <c r="R290" s="12"/>
       <c r="S290" s="13" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="T290" s="13" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="U290" s="14" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="291" spans="1:21">
@@ -20828,7 +20858,7 @@
         <v>422</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C291" s="3" t="s">
         <v>336</v>
@@ -20840,7 +20870,7 @@
         <v>425</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="G291" s="4"/>
       <c r="H291" s="3">
@@ -20871,13 +20901,13 @@
       <c r="Q291" s="5"/>
       <c r="R291" s="6"/>
       <c r="S291" s="3" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="T291" s="3" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="U291" s="7" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="292" spans="1:21">
@@ -20885,10 +20915,10 @@
         <v>422</v>
       </c>
       <c r="B292" s="15" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C292" s="15" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D292" s="15">
         <v>137</v>
@@ -20897,7 +20927,7 @@
         <v>425</v>
       </c>
       <c r="F292" s="15" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="G292" s="16"/>
       <c r="H292" s="15">
@@ -20932,13 +20962,13 @@
       </c>
       <c r="R292" s="6"/>
       <c r="S292" s="3" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="T292" s="3" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="U292" s="7" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="293" spans="1:21">
@@ -20946,10 +20976,10 @@
         <v>422</v>
       </c>
       <c r="B293" s="13" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C293" s="13" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D293" s="13">
         <v>603</v>
@@ -20958,10 +20988,10 @@
         <v>425</v>
       </c>
       <c r="F293" s="13" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="G293" s="17" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H293" s="13">
         <v>8</v>
@@ -20993,13 +21023,13 @@
       </c>
       <c r="R293" s="12"/>
       <c r="S293" s="13" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="T293" s="13" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="U293" s="14" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="294" spans="1:21">
@@ -21007,10 +21037,10 @@
         <v>422</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D294" s="3">
         <v>603</v>
@@ -21019,7 +21049,7 @@
         <v>425</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="G294" s="4"/>
       <c r="H294" s="3">
@@ -21050,13 +21080,13 @@
       <c r="Q294" s="5"/>
       <c r="R294" s="6"/>
       <c r="S294" s="3" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="T294" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="U294" s="7" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="295" spans="1:21">
@@ -21064,7 +21094,7 @@
         <v>422</v>
       </c>
       <c r="B295" s="9" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C295" s="9" t="s">
         <v>350</v>
@@ -21076,10 +21106,10 @@
         <v>425</v>
       </c>
       <c r="F295" s="9" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="G295" s="10" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H295" s="9">
         <v>7741</v>
@@ -21111,13 +21141,13 @@
       </c>
       <c r="R295" s="12"/>
       <c r="S295" s="13" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="T295" s="13" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="U295" s="14" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="296" spans="1:21">
@@ -21125,7 +21155,7 @@
         <v>422</v>
       </c>
       <c r="B296" s="9" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C296" s="9" t="s">
         <v>350</v>
@@ -21137,10 +21167,10 @@
         <v>425</v>
       </c>
       <c r="F296" s="9" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G296" s="10" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H296" s="9">
         <v>1116</v>
@@ -21170,13 +21200,13 @@
       <c r="Q296" s="11"/>
       <c r="R296" s="12"/>
       <c r="S296" s="13" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="T296" s="13" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="U296" s="14" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="297" spans="1:21">
@@ -21184,7 +21214,7 @@
         <v>422</v>
       </c>
       <c r="B297" s="9" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C297" s="9" t="s">
         <v>350</v>
@@ -21196,7 +21226,7 @@
         <v>425</v>
       </c>
       <c r="F297" s="9" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="G297" s="10"/>
       <c r="H297" s="9">
@@ -21225,13 +21255,13 @@
       <c r="Q297" s="11"/>
       <c r="R297" s="12"/>
       <c r="S297" s="13" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="T297" s="13" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="U297" s="14" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="298" spans="1:21">
@@ -21239,7 +21269,7 @@
         <v>422</v>
       </c>
       <c r="B298" s="15" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C298" s="15" t="s">
         <v>350</v>
@@ -21251,10 +21281,10 @@
         <v>425</v>
       </c>
       <c r="F298" s="15" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="G298" s="16" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H298" s="15">
         <v>61</v>
@@ -21282,13 +21312,13 @@
       <c r="Q298" s="5"/>
       <c r="R298" s="6"/>
       <c r="S298" s="3" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="T298" s="3" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="U298" s="7" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="299" spans="1:21">
@@ -21296,10 +21326,10 @@
         <v>422</v>
       </c>
       <c r="B299" s="13" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C299" s="13" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D299" s="13">
         <v>951</v>
@@ -21308,10 +21338,10 @@
         <v>425</v>
       </c>
       <c r="F299" s="13" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="G299" s="17" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H299" s="13">
         <v>174</v>
@@ -21339,13 +21369,13 @@
       <c r="Q299" s="11"/>
       <c r="R299" s="12"/>
       <c r="S299" s="13" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="T299" s="13" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="U299" s="14" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="300" spans="1:21">
@@ -21353,10 +21383,10 @@
         <v>422</v>
       </c>
       <c r="B300" s="13" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C300" s="13" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D300" s="13">
         <v>951</v>
@@ -21365,10 +21395,10 @@
         <v>425</v>
       </c>
       <c r="F300" s="13" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G300" s="17" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H300" s="13">
         <v>322</v>
@@ -21398,13 +21428,13 @@
       <c r="Q300" s="11"/>
       <c r="R300" s="12"/>
       <c r="S300" s="13" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="T300" s="13" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="U300" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="301" spans="1:21">
@@ -21412,10 +21442,10 @@
         <v>422</v>
       </c>
       <c r="B301" s="13" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C301" s="13" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D301" s="13">
         <v>951</v>
@@ -21424,10 +21454,10 @@
         <v>425</v>
       </c>
       <c r="F301" s="13" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="G301" s="17" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H301" s="13">
         <v>30</v>
@@ -21455,13 +21485,13 @@
       <c r="Q301" s="11"/>
       <c r="R301" s="12"/>
       <c r="S301" s="13" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="T301" s="13" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="U301" s="14" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="302" spans="1:21" ht="30.75">
@@ -21469,10 +21499,10 @@
         <v>422</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D302" s="3">
         <v>951</v>
@@ -21481,7 +21511,7 @@
         <v>425</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="G302" s="4"/>
       <c r="H302" s="3">
@@ -21513,16 +21543,16 @@
         <v>46307</v>
       </c>
       <c r="R302" s="6" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="S302" s="3" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="T302" s="3" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="U302" s="7" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="303" spans="1:21">
@@ -21530,10 +21560,10 @@
         <v>422</v>
       </c>
       <c r="B303" s="15" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D303" s="15">
         <v>213</v>
@@ -21542,7 +21572,7 @@
         <v>425</v>
       </c>
       <c r="F303" s="15" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="G303" s="16"/>
       <c r="H303" s="15">
@@ -21577,13 +21607,13 @@
         <v>482</v>
       </c>
       <c r="S303" s="3" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="T303" s="3" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="U303" s="7" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="304" spans="1:21">
@@ -21591,10 +21621,10 @@
         <v>422</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D304" s="3">
         <v>62</v>
@@ -21603,7 +21633,7 @@
         <v>425</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="G304" s="4"/>
       <c r="H304" s="3">
@@ -21638,13 +21668,13 @@
       </c>
       <c r="R304" s="6"/>
       <c r="S304" s="3" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="T304" s="3" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="U304" s="7" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="305" spans="1:21">
@@ -21652,10 +21682,10 @@
         <v>422</v>
       </c>
       <c r="B305" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C305" s="9" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D305" s="9">
         <v>208</v>
@@ -21664,10 +21694,10 @@
         <v>425</v>
       </c>
       <c r="F305" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G305" s="10" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H305" s="9">
         <v>511</v>
@@ -21701,13 +21731,13 @@
       </c>
       <c r="R305" s="12"/>
       <c r="S305" s="13" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="T305" s="13" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="U305" s="14" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="306" spans="1:21">
@@ -21715,10 +21745,10 @@
         <v>422</v>
       </c>
       <c r="B306" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C306" s="9" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D306" s="9">
         <v>208</v>
@@ -21727,10 +21757,10 @@
         <v>425</v>
       </c>
       <c r="F306" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G306" s="10" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H306" s="9">
         <v>283</v>
@@ -21758,13 +21788,13 @@
       <c r="Q306" s="11"/>
       <c r="R306" s="12"/>
       <c r="S306" s="13" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="T306" s="13" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="U306" s="14" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="307" spans="1:21">
@@ -21772,10 +21802,10 @@
         <v>422</v>
       </c>
       <c r="B307" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C307" s="9" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D307" s="9">
         <v>208</v>
@@ -21784,7 +21814,7 @@
         <v>425</v>
       </c>
       <c r="F307" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G307" s="10"/>
       <c r="H307" s="9">
@@ -21813,13 +21843,13 @@
       <c r="Q307" s="11"/>
       <c r="R307" s="12"/>
       <c r="S307" s="13" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="T307" s="13" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="U307" s="14" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="308" spans="1:21">
@@ -21827,10 +21857,10 @@
         <v>422</v>
       </c>
       <c r="B308" s="15" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C308" s="15" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D308" s="15">
         <v>208</v>
@@ -21839,7 +21869,7 @@
         <v>425</v>
       </c>
       <c r="F308" s="15" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G308" s="16"/>
       <c r="H308" s="15">
@@ -21861,20 +21891,22 @@
         <v>0.21</v>
       </c>
       <c r="N308" s="15"/>
-      <c r="O308" s="5"/>
+      <c r="O308" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="P308" s="5"/>
       <c r="Q308" s="5"/>
       <c r="R308" s="6" t="s">
         <v>109</v>
       </c>
       <c r="S308" s="3" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="T308" s="3" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="U308" s="7" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="309" spans="1:21">
@@ -21882,10 +21914,10 @@
         <v>422</v>
       </c>
       <c r="B309" s="13" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C309" s="13" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D309" s="13">
         <v>98</v>
@@ -21894,10 +21926,10 @@
         <v>425</v>
       </c>
       <c r="F309" s="13" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="G309" s="17" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H309" s="13">
         <v>113</v>
@@ -21929,13 +21961,13 @@
       </c>
       <c r="R309" s="12"/>
       <c r="S309" s="13" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="T309" s="13" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="U309" s="14" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="310" spans="1:21">
@@ -21943,10 +21975,10 @@
         <v>422</v>
       </c>
       <c r="B310" s="13" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C310" s="13" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D310" s="13">
         <v>98</v>
@@ -21955,10 +21987,10 @@
         <v>425</v>
       </c>
       <c r="F310" s="13" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="G310" s="17" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H310" s="13">
         <v>95</v>
@@ -21988,13 +22020,13 @@
       <c r="Q310" s="11"/>
       <c r="R310" s="12"/>
       <c r="S310" s="13" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="T310" s="13" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="U310" s="14" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="311" spans="1:21">
@@ -22002,10 +22034,10 @@
         <v>422</v>
       </c>
       <c r="B311" s="13" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C311" s="13" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D311" s="13">
         <v>98</v>
@@ -22014,10 +22046,10 @@
         <v>425</v>
       </c>
       <c r="F311" s="13" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G311" s="17" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H311" s="13">
         <v>1</v>
@@ -22045,13 +22077,13 @@
       <c r="Q311" s="11"/>
       <c r="R311" s="12"/>
       <c r="S311" s="13" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="T311" s="13" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="U311" s="14" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="312" spans="1:21">
@@ -22059,10 +22091,10 @@
         <v>422</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D312" s="3">
         <v>98</v>
@@ -22071,7 +22103,7 @@
         <v>425</v>
       </c>
       <c r="F312" s="3" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="G312" s="4"/>
       <c r="H312" s="3">
@@ -22100,13 +22132,13 @@
       <c r="Q312" s="5"/>
       <c r="R312" s="6"/>
       <c r="S312" s="3" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="T312" s="3" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="U312" s="7" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="313" spans="1:21">
@@ -22114,10 +22146,10 @@
         <v>422</v>
       </c>
       <c r="B313" s="15" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C313" s="15" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D313" s="15">
         <v>1185</v>
@@ -22126,7 +22158,7 @@
         <v>425</v>
       </c>
       <c r="F313" s="15" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G313" s="16"/>
       <c r="H313" s="15">
@@ -22161,13 +22193,13 @@
       </c>
       <c r="R313" s="6"/>
       <c r="S313" s="3" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="T313" s="3" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="U313" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="314" spans="1:21">
@@ -22175,10 +22207,10 @@
         <v>422</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D314" s="3">
         <v>125</v>
@@ -22187,10 +22219,10 @@
         <v>425</v>
       </c>
       <c r="F314" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G314" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H314" s="3">
         <v>201</v>
@@ -22224,13 +22256,13 @@
       </c>
       <c r="R314" s="6"/>
       <c r="S314" s="3" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="T314" s="3" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="U314" s="7" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="315" spans="1:21">
@@ -22238,10 +22270,10 @@
         <v>422</v>
       </c>
       <c r="B315" s="15" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C315" s="15" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D315" s="15">
         <v>2565</v>
@@ -22250,7 +22282,7 @@
         <v>425</v>
       </c>
       <c r="F315" s="15" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="G315" s="16"/>
       <c r="H315" s="15">
@@ -22282,16 +22314,16 @@
         <v>46307</v>
       </c>
       <c r="R315" s="6" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="S315" s="3" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="T315" s="3" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="U315" s="7" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="316" spans="1:21">
@@ -22299,10 +22331,10 @@
         <v>422</v>
       </c>
       <c r="B316" s="13" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C316" s="13" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D316" s="13">
         <v>215</v>
@@ -22311,10 +22343,10 @@
         <v>425</v>
       </c>
       <c r="F316" s="13" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="G316" s="17" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H316" s="13">
         <v>55</v>
@@ -22346,13 +22378,13 @@
       </c>
       <c r="R316" s="12"/>
       <c r="S316" s="13" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="T316" s="13" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="U316" s="14" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="317" spans="1:21">
@@ -22360,10 +22392,10 @@
         <v>422</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D317" s="3">
         <v>215</v>
@@ -22372,10 +22404,10 @@
         <v>425</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="G317" s="4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H317" s="3">
         <v>83</v>
@@ -22405,13 +22437,13 @@
       <c r="Q317" s="5"/>
       <c r="R317" s="6"/>
       <c r="S317" s="3" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="T317" s="3" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="U317" s="7" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="318" spans="1:21">
@@ -22419,7 +22451,7 @@
         <v>422</v>
       </c>
       <c r="B318" s="15" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C318" s="15" t="s">
         <v>235</v>
@@ -22431,7 +22463,7 @@
         <v>425</v>
       </c>
       <c r="F318" s="15" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G318" s="16"/>
       <c r="H318" s="15">
@@ -22466,13 +22498,13 @@
       </c>
       <c r="R318" s="6"/>
       <c r="S318" s="3" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="T318" s="3" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="U318" s="7" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="319" spans="1:21">
@@ -22480,7 +22512,7 @@
         <v>422</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C319" s="3" t="s">
         <v>182</v>
@@ -22492,10 +22524,10 @@
         <v>425</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H319" s="3">
         <v>132</v>
@@ -22529,13 +22561,13 @@
       </c>
       <c r="R319" s="6"/>
       <c r="S319" s="3" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="T319" s="3" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="U319" s="7" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="320" spans="1:21">
@@ -22543,10 +22575,10 @@
         <v>422</v>
       </c>
       <c r="B320" s="9" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C320" s="9" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D320" s="9">
         <v>388</v>
@@ -22555,7 +22587,7 @@
         <v>425</v>
       </c>
       <c r="F320" s="9" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G320" s="10"/>
       <c r="H320" s="9">
@@ -22588,13 +22620,13 @@
       </c>
       <c r="R320" s="12"/>
       <c r="S320" s="13" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="T320" s="13" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="U320" s="14" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="321" spans="1:21">
@@ -22602,10 +22634,10 @@
         <v>422</v>
       </c>
       <c r="B321" s="15" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C321" s="15" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D321" s="15">
         <v>388</v>
@@ -22614,7 +22646,7 @@
         <v>425</v>
       </c>
       <c r="F321" s="15" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G321" s="16"/>
       <c r="H321" s="15">
@@ -22645,21 +22677,21 @@
       <c r="Q321" s="5"/>
       <c r="R321" s="6"/>
       <c r="S321" s="3" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="T321" s="3" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="U321" s="7" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="322" spans="1:21">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="322" spans="1:21" ht="30.75">
       <c r="A322" s="8" t="s">
         <v>422</v>
       </c>
       <c r="B322" s="13" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C322" s="13" t="s">
         <v>127</v>
@@ -22671,10 +22703,10 @@
         <v>425</v>
       </c>
       <c r="F322" s="13" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="G322" s="17" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H322" s="13">
         <v>48</v>
@@ -22697,18 +22729,26 @@
       <c r="N322" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="O322" s="11"/>
-      <c r="P322" s="11"/>
-      <c r="Q322" s="11"/>
-      <c r="R322" s="12"/>
+      <c r="O322" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="P322" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q322" s="21">
+        <v>46308</v>
+      </c>
+      <c r="R322" s="12" t="s">
+        <v>1052</v>
+      </c>
       <c r="S322" s="13" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="T322" s="13" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="U322" s="14" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="323" spans="1:21">
@@ -22716,7 +22756,7 @@
         <v>422</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C323" s="3" t="s">
         <v>127</v>
@@ -22728,10 +22768,10 @@
         <v>425</v>
       </c>
       <c r="F323" s="3" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="H323" s="3">
         <v>29</v>
@@ -22752,18 +22792,20 @@
         <v>2.0699999999999998</v>
       </c>
       <c r="N323" s="3"/>
-      <c r="O323" s="5"/>
+      <c r="O323" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="P323" s="5"/>
       <c r="Q323" s="5"/>
       <c r="R323" s="6"/>
       <c r="S323" s="3" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="T323" s="3" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="U323" s="7" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="324" spans="1:21">
@@ -22771,10 +22813,10 @@
         <v>422</v>
       </c>
       <c r="B324" s="15" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C324" s="15" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D324" s="15">
         <v>0</v>
@@ -22783,7 +22825,7 @@
         <v>425</v>
       </c>
       <c r="F324" s="15" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="G324" s="16"/>
       <c r="H324" s="15">
@@ -22816,13 +22858,13 @@
       </c>
       <c r="R324" s="6"/>
       <c r="S324" s="3" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="T324" s="3" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="U324" s="7" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="325" spans="1:21">
@@ -22830,7 +22872,7 @@
         <v>422</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C325" s="3" t="s">
         <v>508</v>
@@ -22842,7 +22884,7 @@
         <v>425</v>
       </c>
       <c r="F325" s="3" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="G325" s="4"/>
       <c r="H325" s="3">
@@ -22877,13 +22919,13 @@
         <v>482</v>
       </c>
       <c r="S325" s="3" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="T325" s="3" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="U325" s="7" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="326" spans="1:21">
@@ -22891,10 +22933,10 @@
         <v>422</v>
       </c>
       <c r="B326" s="9" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C326" s="9" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D326" s="9">
         <v>406</v>
@@ -22903,10 +22945,10 @@
         <v>425</v>
       </c>
       <c r="F326" s="9" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="G326" s="10" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="H326" s="9">
         <v>462</v>
@@ -22940,13 +22982,13 @@
       </c>
       <c r="R326" s="12"/>
       <c r="S326" s="13" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="T326" s="13" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="U326" s="14" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="327" spans="1:21">
@@ -22954,10 +22996,10 @@
         <v>422</v>
       </c>
       <c r="B327" s="15" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C327" s="15" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D327" s="15">
         <v>406</v>
@@ -22966,10 +23008,10 @@
         <v>425</v>
       </c>
       <c r="F327" s="15" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G327" s="16" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="H327" s="15">
         <v>247</v>
@@ -22997,13 +23039,13 @@
       <c r="Q327" s="5"/>
       <c r="R327" s="6"/>
       <c r="S327" s="3" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="T327" s="3" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="U327" s="7" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="328" spans="1:21">
@@ -23011,7 +23053,7 @@
         <v>422</v>
       </c>
       <c r="B328" s="13" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C328" s="13" t="s">
         <v>193</v>
@@ -23023,10 +23065,10 @@
         <v>425</v>
       </c>
       <c r="F328" s="13" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G328" s="17" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="H328" s="13">
         <v>166</v>
@@ -23060,13 +23102,13 @@
       </c>
       <c r="R328" s="12"/>
       <c r="S328" s="13" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="T328" s="13" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="U328" s="14" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="329" spans="1:21">
@@ -23074,7 +23116,7 @@
         <v>422</v>
       </c>
       <c r="B329" s="13" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C329" s="13" t="s">
         <v>193</v>
@@ -23086,7 +23128,7 @@
         <v>425</v>
       </c>
       <c r="F329" s="13" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="G329" s="17"/>
       <c r="H329" s="13">
@@ -23115,13 +23157,13 @@
       <c r="Q329" s="11"/>
       <c r="R329" s="12"/>
       <c r="S329" s="13" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="T329" s="13" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="U329" s="14" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="330" spans="1:21">
@@ -23129,7 +23171,7 @@
         <v>422</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C330" s="3" t="s">
         <v>193</v>
@@ -23141,7 +23183,7 @@
         <v>425</v>
       </c>
       <c r="F330" s="3" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G330" s="4"/>
       <c r="H330" s="3">
@@ -23170,13 +23212,13 @@
       <c r="Q330" s="5"/>
       <c r="R330" s="6"/>
       <c r="S330" s="3" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="T330" s="3" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="U330" s="7" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="331" spans="1:21">
@@ -23184,10 +23226,10 @@
         <v>422</v>
       </c>
       <c r="B331" s="9" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C331" s="9" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="D331" s="9">
         <v>54</v>
@@ -23196,7 +23238,7 @@
         <v>425</v>
       </c>
       <c r="F331" s="9" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="G331" s="10"/>
       <c r="H331" s="9">
@@ -23231,13 +23273,13 @@
         <v>524</v>
       </c>
       <c r="S331" s="13" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="T331" s="13" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="U331" s="14" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="332" spans="1:21">
@@ -23245,10 +23287,10 @@
         <v>422</v>
       </c>
       <c r="B332" s="15" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C332" s="15" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="D332" s="15">
         <v>54</v>
@@ -23257,7 +23299,7 @@
         <v>425</v>
       </c>
       <c r="F332" s="15" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="G332" s="16"/>
       <c r="H332" s="15">
@@ -23286,13 +23328,13 @@
       <c r="Q332" s="5"/>
       <c r="R332" s="6"/>
       <c r="S332" s="3" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="T332" s="3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="U332" s="7" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="333" spans="1:21">
@@ -23300,7 +23342,7 @@
         <v>422</v>
       </c>
       <c r="B333" s="13" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C333" s="13" t="s">
         <v>563</v>
@@ -23312,7 +23354,7 @@
         <v>425</v>
       </c>
       <c r="F333" s="13" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="G333" s="17"/>
       <c r="H333" s="13">
@@ -23341,13 +23383,13 @@
       <c r="Q333" s="11"/>
       <c r="R333" s="12"/>
       <c r="S333" s="13" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="T333" s="13" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="U333" s="14" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="334" spans="1:21">
@@ -23355,7 +23397,7 @@
         <v>422</v>
       </c>
       <c r="B334" s="13" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C334" s="13" t="s">
         <v>563</v>
@@ -23367,10 +23409,10 @@
         <v>425</v>
       </c>
       <c r="F334" s="13" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="G334" s="17" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="H334" s="13">
         <v>396</v>
@@ -23398,13 +23440,13 @@
       <c r="Q334" s="11"/>
       <c r="R334" s="12"/>
       <c r="S334" s="13" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="T334" s="13" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="U334" s="14" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="335" spans="1:21">
@@ -23412,7 +23454,7 @@
         <v>422</v>
       </c>
       <c r="B335" s="13" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C335" s="13" t="s">
         <v>563</v>
@@ -23424,10 +23466,10 @@
         <v>425</v>
       </c>
       <c r="F335" s="13" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="G335" s="17" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="H335" s="13">
         <v>11</v>
@@ -23455,13 +23497,13 @@
       <c r="Q335" s="11"/>
       <c r="R335" s="12"/>
       <c r="S335" s="13" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="T335" s="13" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="U335" s="14" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="336" spans="1:21">
@@ -23469,7 +23511,7 @@
         <v>422</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C336" s="3" t="s">
         <v>563</v>
@@ -23481,7 +23523,7 @@
         <v>425</v>
       </c>
       <c r="F336" s="3" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="G336" s="4"/>
       <c r="H336" s="3">
@@ -23512,13 +23554,13 @@
       <c r="Q336" s="5"/>
       <c r="R336" s="6"/>
       <c r="S336" s="3" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="T336" s="3" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="U336" s="7" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="337" spans="1:21">
@@ -23526,10 +23568,10 @@
         <v>422</v>
       </c>
       <c r="B337" s="15" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C337" s="15" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D337" s="15">
         <v>176</v>
@@ -23538,10 +23580,10 @@
         <v>425</v>
       </c>
       <c r="F337" s="15" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="G337" s="16" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="H337" s="15">
         <v>108</v>
@@ -23571,13 +23613,13 @@
       <c r="Q337" s="5"/>
       <c r="R337" s="6"/>
       <c r="S337" s="3" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="T337" s="3" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="U337" s="7" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -23939,12 +23981,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="18" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="60.75">
       <c r="A2" s="19" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -23952,12 +23994,12 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="18" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="19" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -23965,12 +24007,12 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="18" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="19" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -23978,27 +24020,27 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="18" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="19" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="19" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="19" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="19" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -24006,32 +24048,32 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="18" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="19" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="19" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="19" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="19" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="19" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -24039,12 +24081,12 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="19" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -24052,17 +24094,17 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="18" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="19" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="19" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
     </row>
   </sheetData>
